--- a/Datos 03.01 - J.xlsx
+++ b/Datos 03.01 - J.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Cursos\Introduccion a la Ciencia de Datos\GitHub\EP1053\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F4E2ED-326F-4F4E-B423-683BBC74B9C4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CASOS_10082020" sheetId="1" r:id="rId1"/>
@@ -133,7 +134,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -967,7 +968,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1517,7 +1518,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1543,10 +1544,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1160384</v>
+        <v>3023137</v>
       </c>
       <c r="D2">
-        <v>224836</v>
+        <v>484574</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1557,10 +1558,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>92136</v>
+        <v>218793</v>
       </c>
       <c r="D3">
-        <v>23090</v>
+        <v>49195</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1571,10 +1572,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>98605</v>
+        <v>207188</v>
       </c>
       <c r="D4">
-        <v>17669</v>
+        <v>40548</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1585,10 +1586,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>147532</v>
+        <v>387908</v>
       </c>
       <c r="D5">
-        <v>19883</v>
+        <v>54222</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -1599,10 +1600,10 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>45329</v>
+        <v>136034</v>
       </c>
       <c r="D6">
-        <v>4745</v>
+        <v>18179</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -1613,10 +1614,10 @@
         <v>12</v>
       </c>
       <c r="C7">
-        <v>58541</v>
+        <v>191278</v>
       </c>
       <c r="D7">
-        <v>6879</v>
+        <v>29337</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -1627,10 +1628,10 @@
         <v>13</v>
       </c>
       <c r="C8">
-        <v>79749</v>
+        <v>171575</v>
       </c>
       <c r="D8">
-        <v>18875</v>
+        <v>36116</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -1641,10 +1642,10 @@
         <v>14</v>
       </c>
       <c r="C9">
-        <v>90985</v>
+        <v>196609</v>
       </c>
       <c r="D9">
-        <v>22736</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -1655,10 +1656,10 @@
         <v>15</v>
       </c>
       <c r="C10">
-        <v>38430</v>
+        <v>90384</v>
       </c>
       <c r="D10">
-        <v>7125</v>
+        <v>19763</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -1669,10 +1670,10 @@
         <v>16</v>
       </c>
       <c r="C11">
-        <v>79740</v>
+        <v>169681</v>
       </c>
       <c r="D11">
-        <v>14906</v>
+        <v>35307</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1683,10 +1684,10 @@
         <v>17</v>
       </c>
       <c r="C12">
-        <v>64445</v>
+        <v>213161</v>
       </c>
       <c r="D12">
-        <v>9723</v>
+        <v>36138</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -1697,10 +1698,10 @@
         <v>18</v>
       </c>
       <c r="C13">
-        <v>77959</v>
+        <v>204072</v>
       </c>
       <c r="D13">
-        <v>14068</v>
+        <v>35125</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -1711,10 +1712,10 @@
         <v>19</v>
       </c>
       <c r="C14">
-        <v>60335</v>
+        <v>170309</v>
       </c>
       <c r="D14">
-        <v>8616</v>
+        <v>29263</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -1725,10 +1726,10 @@
         <v>20</v>
       </c>
       <c r="C15">
-        <v>47344</v>
+        <v>122341</v>
       </c>
       <c r="D15">
-        <v>8190</v>
+        <v>22696</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -1739,10 +1740,10 @@
         <v>21</v>
       </c>
       <c r="C16">
-        <v>28853</v>
+        <v>100082</v>
       </c>
       <c r="D16">
-        <v>1333</v>
+        <v>9651</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1753,10 +1754,10 @@
         <v>22</v>
       </c>
       <c r="C17">
-        <v>41812</v>
+        <v>120522</v>
       </c>
       <c r="D17">
-        <v>3795</v>
+        <v>21560</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1767,10 +1768,10 @@
         <v>23</v>
       </c>
       <c r="C18">
-        <v>43385</v>
+        <v>110709</v>
       </c>
       <c r="D18">
-        <v>4420</v>
+        <v>17187</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1781,10 +1782,10 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>40863</v>
+        <v>83857</v>
       </c>
       <c r="D19">
-        <v>12466</v>
+        <v>27432</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1795,10 +1796,10 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>53801</v>
+        <v>117980</v>
       </c>
       <c r="D20">
-        <v>10215</v>
+        <v>28021</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1809,10 +1810,10 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>34044</v>
+        <v>91765</v>
       </c>
       <c r="D21">
-        <v>5033</v>
+        <v>16831</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1823,10 +1824,10 @@
         <v>27</v>
       </c>
       <c r="C22">
-        <v>25312</v>
+        <v>67281</v>
       </c>
       <c r="D22">
-        <v>2436</v>
+        <v>8529</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1837,10 +1838,10 @@
         <v>28</v>
       </c>
       <c r="C23">
-        <v>26028</v>
+        <v>65018</v>
       </c>
       <c r="D23">
-        <v>2628</v>
+        <v>8023</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1851,10 +1852,10 @@
         <v>29</v>
       </c>
       <c r="C24">
-        <v>21590</v>
+        <v>54619</v>
       </c>
       <c r="D24">
-        <v>4711</v>
+        <v>10414</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1865,10 +1866,10 @@
         <v>30</v>
       </c>
       <c r="C25">
-        <v>35481</v>
+        <v>75998</v>
       </c>
       <c r="D25">
-        <v>10993</v>
+        <v>21615</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1879,10 +1880,10 @@
         <v>31</v>
       </c>
       <c r="C26">
-        <v>24040</v>
+        <v>49625</v>
       </c>
       <c r="D26">
-        <v>4078</v>
+        <v>9823</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1893,10 +1894,10 @@
         <v>32</v>
       </c>
       <c r="C27">
-        <v>73355</v>
+        <v>196207</v>
       </c>
       <c r="D27">
-        <v>19684</v>
+        <v>35993</v>
       </c>
     </row>
   </sheetData>
